--- a/data/trans_orig/P79A10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A10_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>25391</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>31998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>54450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66834</t>
+          <t>77151</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>64229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72368</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>88775</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>76980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85996</t>
+          <t>96286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50939</t>
+          <t>59880</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>49765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57424</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>129746</t>
+          <t>148654</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114894</t>
+          <t>135854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140393</t>
+          <t>159112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46638</t>
+          <t>46848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93681</t>
+          <t>104060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93681</t>
+          <t>104060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93681</t>
+          <t>104060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>78643</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>78643</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>78643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>182702</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>182702</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>182702</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120296</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>103497</t>
+          <t>120360</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>108837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111253</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>214748</t>
+          <t>248009</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196269</t>
+          <t>229941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227843</t>
+          <t>261933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>29957</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
